--- a/pre-inscritos/preinscritos.xlsx
+++ b/pre-inscritos/preinscritos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\GITHUB\trabajocientifico\curso-profesional-ciencia-de-datos\pre-inscritos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C002DB2-BE5F-4A00-BC37-282DEBB68FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED8746A-7D5E-4AF5-B5AC-469B7924D816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8CB47D37-B596-4B1F-AD8C-CDD6FAF132B9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="247">
   <si>
     <t>Julian Andrés Pérez Ortega</t>
   </si>
@@ -727,13 +727,67 @@
   </si>
   <si>
     <t>Estado</t>
+  </si>
+  <si>
+    <t>ritesh7739128515@gmail.com</t>
+  </si>
+  <si>
+    <t>Ritesh kumar</t>
+  </si>
+  <si>
+    <t>Pedro Luis Collazo Abreu</t>
+  </si>
+  <si>
+    <t>pedrocollazo1988@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veronica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kely Hincapie </t>
+  </si>
+  <si>
+    <t>kjhincapie6@gmail.com</t>
+  </si>
+  <si>
+    <t>Luis Eduardo</t>
+  </si>
+  <si>
+    <t>lriascos45@yahoo.es</t>
+  </si>
+  <si>
+    <t>ANGEL RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>angelrodrich@gmail.com</t>
+  </si>
+  <si>
+    <t>Mateo Agudelo</t>
+  </si>
+  <si>
+    <t>amagudelo@unillanos.edu.co</t>
+  </si>
+  <si>
+    <t>Andrés Felipe Villadiego arteaga</t>
+  </si>
+  <si>
+    <t>andresf.villadiego@gmail.com</t>
+  </si>
+  <si>
+    <t>Patt</t>
+  </si>
+  <si>
+    <t>sadupa2@gmail.com</t>
+  </si>
+  <si>
+    <t>Kely Hincapie</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,6 +799,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -779,16 +841,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1143,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F727EEDE-3999-42D5-8EEF-A46E78C9F3F0}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -1778,6 +1843,39 @@
         <v>114</v>
       </c>
     </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1785,7 +1883,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C5F129-18F1-40A7-82FC-61684AE0E6F5}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -2643,7 +2741,90 @@
         <v>En curso</v>
       </c>
     </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>231</v>
+      </c>
+      <c r="B74" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>234</v>
+      </c>
+      <c r="B76" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>236</v>
+      </c>
+      <c r="B77" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>240</v>
+      </c>
+      <c r="B79" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>242</v>
+      </c>
+      <c r="B80" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>244</v>
+      </c>
+      <c r="B81" t="s">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B72" r:id="rId1" xr:uid="{64F31F35-64B0-432E-A2DE-EEC5A19EAB65}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pre-inscritos/preinscritos.xlsx
+++ b/pre-inscritos/preinscritos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\GITHUB\trabajocientifico\curso-profesional-ciencia-de-datos\pre-inscritos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFCE0ED-9143-4552-B616-A49E16170278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDB71D9-5869-4FC3-9AA3-E34AD71FE765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8CB47D37-B596-4B1F-AD8C-CDD6FAF132B9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8CB47D37-B596-4B1F-AD8C-CDD6FAF132B9}"/>
   </bookViews>
   <sheets>
     <sheet name="curso" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="310">
   <si>
     <t>Julian Andrés Pérez Ortega</t>
   </si>
@@ -720,9 +720,6 @@
     <t>Cecilia</t>
   </si>
   <si>
-    <t>Estado</t>
-  </si>
-  <si>
     <t>ritesh7739128515@gmail.com</t>
   </si>
   <si>
@@ -790,13 +787,199 @@
   </si>
   <si>
     <t>aperalta@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>Jorge Luis Aquino Olmos</t>
+  </si>
+  <si>
+    <t>aquinosuarez@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria Alejandra Garzón Sánchez</t>
+  </si>
+  <si>
+    <t>Camilo andres Chacon moreno</t>
+  </si>
+  <si>
+    <t>cami2005.cm@gmail.com</t>
+  </si>
+  <si>
+    <t>Angelica Ricardo</t>
+  </si>
+  <si>
+    <t>angyricar@yahoo.com</t>
+  </si>
+  <si>
+    <t>RICARDO GÓMEZ SUÁREZ</t>
+  </si>
+  <si>
+    <t>r.gomezsu@gmail.com</t>
+  </si>
+  <si>
+    <t>Melina</t>
+  </si>
+  <si>
+    <t>milericar2018@gmail.com</t>
+  </si>
+  <si>
+    <t>VICTORIA INÉS SOTO OSPINO</t>
+  </si>
+  <si>
+    <t>kioratravel@gmail.com</t>
+  </si>
+  <si>
+    <t>Michael Vanoy</t>
+  </si>
+  <si>
+    <t>mvanoy17@uan.edu.co</t>
+  </si>
+  <si>
+    <t>Helena Patricia Luna Serpa</t>
+  </si>
+  <si>
+    <t>helena.corporativo87@gmail.com</t>
+  </si>
+  <si>
+    <t>Denise Hernandez</t>
+  </si>
+  <si>
+    <t>Eduin Culma</t>
+  </si>
+  <si>
+    <t>tomorro91@gmail.com</t>
+  </si>
+  <si>
+    <t>Randy Triana</t>
+  </si>
+  <si>
+    <t>trianarandy@gmail.com</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>eduardotovarmurcia@gmail.com</t>
+  </si>
+  <si>
+    <t>Nini Johana Santanilla</t>
+  </si>
+  <si>
+    <t>johana.santanilla.v@gmail.com</t>
+  </si>
+  <si>
+    <t>paula calderon</t>
+  </si>
+  <si>
+    <t>paucldrn123@gmail.com</t>
+  </si>
+  <si>
+    <t>Daniel Alberto Chacón Alonso</t>
+  </si>
+  <si>
+    <t>252t0664@itsm.edu.mx</t>
+  </si>
+  <si>
+    <t>Maria Claudia Acosta</t>
+  </si>
+  <si>
+    <t>mariace0431@gmail.com</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Perú</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>593 983888398</t>
+  </si>
+  <si>
+    <t>ECUADOR</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>COLOMBIA</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Celular</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Jonathan Puente</t>
+  </si>
+  <si>
+    <t>jspuente.ec@gmail.com</t>
+  </si>
+  <si>
+    <t>Michael Steven Castañeda Mendoza</t>
+  </si>
+  <si>
+    <t>fincasvilla@gmail.com</t>
+  </si>
+  <si>
+    <t>YOLIBE FOREROPINEDA</t>
+  </si>
+  <si>
+    <t>y33379147@gmail.com</t>
+  </si>
+  <si>
+    <t>gaparrado@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrés Parrado</t>
+  </si>
+  <si>
+    <t>erika.zambrano@unillanos.edu.co</t>
+  </si>
+  <si>
+    <t>Alejandra González Galvis</t>
+  </si>
+  <si>
+    <t>gonzalezgalvisalejandra@gmail.com</t>
+  </si>
+  <si>
+    <t>harryvelandia@gmail.com</t>
+  </si>
+  <si>
+    <t>HARRY ALEXANDER VELANDIA BERMUDEZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -829,6 +1012,13 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -872,24 +1062,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Millares" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1225,6 +1426,9 @@
   <wetp:taskpane dockstate="right" visibility="0" width="865" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
 </wetp:taskpanes>
 </file>
 
@@ -1242,1499 +1446,1757 @@
 </we:webextension>
 </file>
 
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{8F82E18B-25DD-4DDF-B560-3075DA81C3DB}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;724040ba-a118-497b-9f76-52f97a09af34&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F727EEDE-3999-42D5-8EEF-A46E78C9F3F0}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="9">
+        <v>3205554519</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="9">
+        <v>3644320100</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="9">
+        <v>51954036682</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="9">
+        <v>3504170603</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="9">
+        <v>573197087680</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="9">
+        <v>584166754940</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="9">
+        <v>526141906172</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="9">
+        <v>3147552147</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="9">
+        <v>3217931762</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="9">
+        <v>3044031663</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" s="9">
+        <v>3178063943</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" s="9">
+        <v>960745088</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" s="9">
+        <v>1122546298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="9">
+        <v>3177148795</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="9">
+        <v>3134249538</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" s="9">
+        <v>573012878456</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" s="9">
+        <v>953993511</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" s="9">
+        <v>573136037966</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" s="9">
+        <v>3057084812</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" s="9">
+        <v>593968806807</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" s="9">
+        <v>3013306037</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" s="9">
+        <v>573202041939</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" s="9">
+        <v>51990268408</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" s="9">
+        <v>3114588869</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" s="9">
+        <v>3164830244</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" s="9">
+        <v>34644392098</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" s="9">
+        <v>573008786742</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" s="9">
+        <v>3008006845</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" s="9">
+        <v>3122683063</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" s="9">
+        <v>3177148795</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="7" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" s="9">
+        <v>3197305747</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="7" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="9">
+        <v>573164325181</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="7" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="9">
+        <v>50251494542</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="9">
+        <v>3133692915</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="9">
+        <v>50688116585</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="7" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" s="9">
+        <v>945862795</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43" s="9">
+        <v>3156252588</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44" s="9">
+        <v>584144336668</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="7" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45" s="9">
+        <v>3125728198</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="7" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46" s="9">
+        <v>375385353</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47" s="9">
+        <v>573210000000</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" s="9">
+        <v>5713122711657</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="7" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49" s="9">
+        <v>573002182184</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50" s="9">
+        <v>5493875557992</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51" s="9">
+        <v>3014212992</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52" s="9">
+        <v>573187088036</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="7" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54" s="9">
+        <v>3124480182</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55" s="9">
+        <v>5577459855</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" s="9">
+        <v>3001204634</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="7" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57" s="9">
+        <v>543875232648</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="9">
+        <v>573015704518</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C59" s="9">
+        <v>573026492778</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="2">
+        <v>3125728198</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="2">
+        <v>3217931762</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C62" s="10">
+        <v>593994044038</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C63" s="2">
+        <v>3219995603</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C5F129-18F1-40A7-82FC-61684AE0E6F5}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B2)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B3)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B4)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B5)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B6)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B7)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B8)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B9)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B10)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B11)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B12)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B13)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B14)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B15)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B16)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B17)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B18)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B19)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B20)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B21)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B22)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B23)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B24)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B25)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B26)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B27)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B28)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B29)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B30)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B31)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C32" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B32)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B33)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B34)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C35" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B35)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B36)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C37" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B37)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C38" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B38)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B39)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B40)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C41" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B41)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B42)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C43" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B43)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C44" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B44)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C45" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B45)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C46" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B46)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C47" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B47)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C48" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B48)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C49" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B49)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C50" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B50)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C51" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B51)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B52)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B53)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C54" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B54)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C55" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B55)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C56" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B56)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B57)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C58" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B58)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C59" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B59)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B60)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C61" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B61)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C62" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B62)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C63" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B63)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C64" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B64)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C65" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B65)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C66" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B66)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C67" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B67)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C68" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B68)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C69" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B69)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C70" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B70)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B71)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C72" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B72)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B73)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C74" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B74)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B75)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C76" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B76)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C77" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B77)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C78" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B78)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C79" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B79)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C80" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B80)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C81" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B81)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C82" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B82)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Taller y curso</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C83" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B83)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C84" s="2" t="str">
-        <f>IF(COUNTIF(curso!$B$2:$B$59,B84)&gt;0,"Taller y curso","Solo taller")</f>
-        <v>Solo taller</v>
+      <c r="B102" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2743,7 +3205,13 @@
     <hyperlink ref="B82" r:id="rId2" xr:uid="{2AB2D34E-C6A4-49A7-9D63-EA933103E415}"/>
     <hyperlink ref="B83" r:id="rId3" xr:uid="{AC8400D8-C2DF-47D4-BD74-B3B9730CCF39}"/>
     <hyperlink ref="B84" r:id="rId4" xr:uid="{C56C9943-C44D-4E8A-B5D7-139DD7F23790}"/>
+    <hyperlink ref="B100" r:id="rId5" xr:uid="{08BF73E0-2336-4EDD-B434-EBBAABE1FDD8}"/>
+    <hyperlink ref="B101" r:id="rId6" xr:uid="{96ADEEC7-816F-46C0-88F0-1AF320F4ECE9}"/>
+    <hyperlink ref="B102" r:id="rId7" xr:uid="{15FE588F-0F4F-470F-AD45-D4DC29D4E20E}"/>
+    <hyperlink ref="B103" r:id="rId8" xr:uid="{151C09E3-8AAA-4AEA-947C-DCB219156901}"/>
+    <hyperlink ref="B104" r:id="rId9" xr:uid="{92051EAD-1118-4AC6-A4AB-F8FF8C9B0B01}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId10"/>
 </worksheet>
 </file>